--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stealth User1\Desktop\Dev_Home\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CA0E222-CAF5-41AB-BC1A-864CC4754211}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA20E31-C77B-442D-B3E5-57D5F7C6820C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -114,9 +114,6 @@
     <t>TextArea</t>
   </si>
   <si>
-    <t>Automation Site Visit Regression</t>
-  </si>
-  <si>
     <t>SvProgramFormQ1__c</t>
   </si>
   <si>
@@ -169,6 +166,9 @@
   </si>
   <si>
     <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
+  </si>
+  <si>
+    <t>Automation Site Visit</t>
   </si>
 </sst>
 </file>
@@ -553,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -777,10 +777,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -788,10 +788,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -799,10 +799,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -810,10 +810,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
         <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -821,10 +821,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -832,10 +832,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -843,10 +843,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -854,10 +854,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
         <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -865,10 +865,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nauman.shahid/Nauman-data/Dev_Home/govgrants-product-automation/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA20E31-C77B-442D-B3E5-57D5F7C6820C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F675D27-1538-E347-876D-800BBE2B70D7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="4000" yWindow="-17560" windowWidth="23260" windowHeight="12580" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>Automation Site Visit</t>
+  </si>
+  <si>
+    <t>SiteVisitType__c</t>
+  </si>
+  <si>
+    <t>Award</t>
   </si>
 </sst>
 </file>
@@ -527,14 +533,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,7 +551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -556,7 +562,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -567,7 +573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -576,6 +582,17 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -586,12 +603,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -599,7 +616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -607,7 +624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -615,7 +632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -623,22 +640,22 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -651,14 +668,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -669,7 +686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -680,7 +697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -691,7 +708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -702,7 +719,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -713,7 +730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -724,7 +741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -735,7 +752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -754,14 +771,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="100.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -772,7 +789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -783,7 +800,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -794,7 +811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,7 +822,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -816,7 +833,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -827,7 +844,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -838,7 +855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -849,7 +866,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -860,7 +877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nauman.shahid/Nauman-data/Dev_Home/govgrants-product-automation/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F675D27-1538-E347-876D-800BBE2B70D7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49227B2D-EFAF-45AA-AB3E-6D604244D98D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4000" yWindow="-17560" windowWidth="23260" windowHeight="12580" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
-    <sheet name="Edition" sheetId="3" r:id="rId3"/>
-    <sheet name="Form Fields" sheetId="5" r:id="rId4"/>
+    <sheet name="Fiscal" sheetId="6" r:id="rId3"/>
+    <sheet name="Edition" sheetId="3" r:id="rId4"/>
+    <sheet name="Form Fields" sheetId="5" r:id="rId5"/>
+    <sheet name="Program" sheetId="7" r:id="rId6"/>
+    <sheet name="Application" sheetId="8" r:id="rId7"/>
+    <sheet name="Award" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="52">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -168,13 +172,22 @@
     <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
   </si>
   <si>
-    <t>Automation Site Visit</t>
-  </si>
-  <si>
     <t>SiteVisitType__c</t>
   </si>
   <si>
     <t>Award</t>
+  </si>
+  <si>
+    <t>Fiscal</t>
+  </si>
+  <si>
+    <t>Automation Site Visit Org level</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Application</t>
   </si>
 </sst>
 </file>
@@ -534,13 +547,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,7 +564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -559,10 +572,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -573,7 +586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -584,15 +597,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
         <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -603,12 +616,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -616,7 +629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -624,7 +637,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -632,7 +645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -640,22 +653,22 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -666,16 +679,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -686,81 +700,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -769,16 +750,119 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -789,7 +873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -800,7 +884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,7 +895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -822,7 +906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -833,7 +917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -844,7 +928,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -855,7 +939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -866,7 +950,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -877,7 +961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -886,6 +970,219 @@
       </c>
       <c r="C10" t="s">
         <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49227B2D-EFAF-45AA-AB3E-6D604244D98D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D05DA1-E5F1-41C3-A761-DBD4A0997D78}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -605,7 +605,7 @@
         <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1040,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D05DA1-E5F1-41C3-A761-DBD4A0997D78}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97342734-CDBC-48E0-9E55-5C0B1014D489}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
     <sheet name="Fiscal" sheetId="6" r:id="rId3"/>
     <sheet name="Edition" sheetId="3" r:id="rId4"/>
-    <sheet name="Form Fields" sheetId="5" r:id="rId5"/>
-    <sheet name="Program" sheetId="7" r:id="rId6"/>
-    <sheet name="Application" sheetId="8" r:id="rId7"/>
-    <sheet name="Award" sheetId="9" r:id="rId8"/>
+    <sheet name="Edition1" sheetId="10" r:id="rId5"/>
+    <sheet name="Form Fields" sheetId="5" r:id="rId6"/>
+    <sheet name="Program" sheetId="7" r:id="rId7"/>
+    <sheet name="Application" sheetId="8" r:id="rId8"/>
+    <sheet name="Award" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="52">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -853,6 +854,88 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -977,7 +1060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1048,7 +1131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1119,7 +1202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97342734-CDBC-48E0-9E55-5C0B1014D489}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE18BA36-18BD-4204-838A-87A8ED1FE5EC}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -611,6 +611,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97342734-CDBC-48E0-9E55-5C0B1014D489}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E93D5C1-390C-479B-AECF-D8E374109045}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="52">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -576,7 +576,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -674,8 +674,17 @@
         <v>27</v>
       </c>
     </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E93D5C1-390C-479B-AECF-D8E374109045}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE61B30-D53D-426A-A018-9D1315CCAFC4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
-    <sheet name="Fiscal" sheetId="6" r:id="rId3"/>
-    <sheet name="Edition" sheetId="3" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="10" r:id="rId5"/>
-    <sheet name="Form Fields" sheetId="5" r:id="rId6"/>
-    <sheet name="Program" sheetId="7" r:id="rId7"/>
-    <sheet name="Application" sheetId="8" r:id="rId8"/>
-    <sheet name="Award" sheetId="9" r:id="rId9"/>
+    <sheet name="Fiscal" sheetId="6" r:id="rId2"/>
+    <sheet name="Edition" sheetId="3" r:id="rId3"/>
+    <sheet name="Edition1" sheetId="10" r:id="rId4"/>
+    <sheet name="Form Fields" sheetId="5" r:id="rId5"/>
+    <sheet name="Program" sheetId="7" r:id="rId6"/>
+    <sheet name="Application" sheetId="8" r:id="rId7"/>
+    <sheet name="Award" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -33,14 +32,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="44">
   <si>
     <t>Sub Tab</t>
   </si>
   <si>
-    <t>Field Type</t>
-  </si>
-  <si>
     <t>Field API Name</t>
   </si>
   <si>
@@ -50,24 +46,15 @@
     <t>None</t>
   </si>
   <si>
-    <t>Text</t>
-  </si>
-  <si>
     <t>Title__c</t>
   </si>
   <si>
-    <t>Lookup</t>
-  </si>
-  <si>
     <t>GranteePOCContact__c</t>
   </si>
   <si>
     <t>Automation SPI</t>
   </si>
   <si>
-    <t>DropDown</t>
-  </si>
-  <si>
     <t>MonitoringType__c</t>
   </si>
   <si>
@@ -77,9 +64,6 @@
     <t>Overview</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>VisitDateandTime__c</t>
   </si>
   <si>
@@ -89,9 +73,6 @@
     <t>Description__c</t>
   </si>
   <si>
-    <t>RichText</t>
-  </si>
-  <si>
     <t>Automation Test description</t>
   </si>
   <si>
@@ -101,9 +82,6 @@
     <t>SiteVisitPurpose__c</t>
   </si>
   <si>
-    <t>Dropdown</t>
-  </si>
-  <si>
     <t>Routine based on monitoring responsibilities</t>
   </si>
   <si>
@@ -114,9 +92,6 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
-    <t>TextArea</t>
   </si>
   <si>
     <t>SvProgramFormQ1__c</t>
@@ -559,127 +534,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -688,7 +590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -704,54 +606,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -759,7 +661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -774,18 +676,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -793,10 +695,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
@@ -804,57 +706,57 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -878,18 +780,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -897,10 +799,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
@@ -908,35 +810,35 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -959,109 +861,109 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1085,54 +987,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1140,7 +1042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1156,54 +1058,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1227,54 +1129,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE61B30-D53D-426A-A018-9D1315CCAFC4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA8128C-333B-4892-9E01-F07DECFFB71C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="45">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>Application</t>
+  </si>
+  <si>
+    <t>Automation spi</t>
   </si>
 </sst>
 </file>
@@ -523,13 +526,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -540,7 +543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -551,7 +554,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -562,7 +565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -573,7 +576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -593,15 +596,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -612,7 +615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -623,7 +626,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -631,10 +634,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -645,7 +648,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -664,14 +667,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -682,7 +685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -693,7 +696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -704,7 +707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -715,7 +718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -726,7 +729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -737,7 +740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -748,7 +751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -767,15 +770,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -786,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -797,7 +800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -808,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -819,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -830,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,14 +852,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -867,7 +870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -878,7 +881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -889,7 +892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -900,7 +903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -911,7 +914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -922,7 +925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -933,7 +936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -944,7 +947,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -955,7 +958,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -974,15 +977,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -993,7 +996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1004,7 +1007,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1045,15 +1048,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1086,7 +1089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1097,7 +1100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1116,15 +1119,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +1138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1146,7 +1149,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA8128C-333B-4892-9E01-F07DECFFB71C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2993788-1F94-4BE4-B6D1-26D13B30517C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="44">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>Application</t>
-  </si>
-  <si>
-    <t>Automation spi</t>
   </si>
 </sst>
 </file>
@@ -526,13 +523,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,7 +540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -554,7 +551,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -565,7 +562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -576,7 +573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -596,15 +593,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -615,7 +612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -626,7 +623,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -634,10 +631,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -648,7 +645,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -667,14 +664,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -685,7 +682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -696,7 +693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -707,7 +704,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -718,7 +715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -729,7 +726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -740,7 +737,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -751,7 +748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -770,15 +767,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -800,7 +797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -811,7 +808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -822,7 +819,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -833,7 +830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -852,14 +849,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -870,7 +867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -881,7 +878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -892,7 +889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -903,7 +900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -914,7 +911,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -925,7 +922,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -936,7 +933,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -947,7 +944,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -958,7 +955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -977,15 +974,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -996,7 +993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1007,7 +1004,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1018,7 +1015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1029,7 +1026,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1048,15 +1045,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +1075,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1119,15 +1116,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1146,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1160,7 +1157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1171,7 +1168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2993788-1F94-4BE4-B6D1-26D13B30517C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB06C70-DC29-4803-BBDC-563B76DF8794}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="45">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>Application</t>
+  </si>
+  <si>
+    <t>Automation Runtime Site Visit Org level</t>
   </si>
 </sst>
 </file>
@@ -526,7 +529,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -548,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB06C70-DC29-4803-BBDC-563B76DF8794}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1566F02-46D7-4703-A66B-30CAE4416562}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>GranteePOCContact__c</t>
   </si>
   <si>
-    <t>Automation SPI</t>
-  </si>
-  <si>
     <t>MonitoringType__c</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>Automation Runtime Site Visit Org level</t>
+  </si>
+  <si>
+    <t>Automation SPI3</t>
   </si>
 </sst>
 </file>
@@ -526,13 +526,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,7 +543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -551,10 +551,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -562,29 +562,29 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -596,15 +596,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -615,7 +615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -623,10 +623,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -634,29 +634,29 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -667,14 +667,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -685,81 +685,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -770,15 +770,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -789,59 +789,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -852,14 +852,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="100.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -870,103 +870,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -977,15 +977,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1004,10 +1004,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1015,29 +1015,29 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1048,15 +1048,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1075,10 +1075,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1086,29 +1086,29 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1119,15 +1119,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1146,10 +1146,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1157,29 +1157,29 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1566F02-46D7-4703-A66B-30CAE4416562}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B00A23F-B958-4D97-9781-24C42EEBB726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -173,13 +173,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -211,6 +217,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,13 +533,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.46484375" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,7 +550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -554,7 +561,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -565,7 +572,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -576,15 +583,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
-        <v>42</v>
+      <c r="C5" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -596,15 +603,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -615,7 +622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -626,7 +633,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -637,7 +644,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -648,7 +655,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -667,14 +674,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -685,7 +692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -696,7 +703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -707,7 +714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -718,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -729,7 +736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -740,7 +747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -751,7 +758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -770,15 +777,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -789,7 +796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -800,7 +807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -811,7 +818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -822,7 +829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,7 +840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -852,14 +859,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="100.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -870,7 +877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -881,7 +888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -892,7 +899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -903,7 +910,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -914,7 +921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -925,7 +932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -936,7 +943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -947,7 +954,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -958,7 +965,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -977,15 +984,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -996,7 +1003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1007,7 +1014,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1018,7 +1025,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1029,7 +1036,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1048,15 +1055,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +1085,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1096,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1119,15 +1126,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1156,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1160,7 +1167,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1171,7 +1178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B00A23F-B958-4D97-9781-24C42EEBB726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2B56A3-7028-4E68-9B61-925ACEEE7224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -46,51 +46,21 @@
     <t>None</t>
   </si>
   <si>
-    <t>Title__c</t>
-  </si>
-  <si>
-    <t>GranteePOCContact__c</t>
-  </si>
-  <si>
-    <t>MonitoringType__c</t>
-  </si>
-  <si>
     <t>Program &amp; Fiscal</t>
   </si>
   <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>VisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>VisitEndDateTime__c</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>Automation Test description</t>
   </si>
   <si>
-    <t>Pointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>SiteVisitPurpose__c</t>
-  </si>
-  <si>
     <t>Routine based on monitoring responsibilities</t>
   </si>
   <si>
-    <t>SourceSiteVisit__c</t>
-  </si>
-  <si>
     <t>To fulfill pass-through monitoring responsibilities</t>
   </si>
   <si>
-    <t>SupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
     <t>SvProgramFormQ1__c</t>
   </si>
   <si>
@@ -145,9 +115,6 @@
     <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
   </si>
   <si>
-    <t>SiteVisitType__c</t>
-  </si>
-  <si>
     <t>Award</t>
   </si>
   <si>
@@ -167,6 +134,39 @@
   </si>
   <si>
     <t>Automation SPI3</t>
+  </si>
+  <si>
+    <t>fieldVisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>fieldVisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldPointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>fieldSiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>fieldSourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>fieldSupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldGranteePOCContact__c</t>
+  </si>
+  <si>
+    <t>fieldMonitoringType__c</t>
+  </si>
+  <si>
+    <t>fieldSiteVisitType__c</t>
   </si>
 </sst>
 </file>
@@ -554,44 +554,44 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+      <c r="B4" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>37</v>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -606,7 +606,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
@@ -626,44 +626,44 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+      <c r="B4" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>37</v>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -694,10 +694,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -705,10 +705,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
@@ -716,57 +716,57 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -798,10 +798,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -809,10 +809,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
@@ -820,35 +820,35 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -882,10 +882,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -893,10 +893,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -904,10 +904,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -926,10 +926,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -937,10 +937,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -948,10 +948,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -959,10 +959,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -970,10 +970,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1007,44 +1007,44 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+      <c r="B4" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>37</v>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1078,44 +1078,44 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+      <c r="B4" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>37</v>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1149,44 +1149,44 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+      <c r="B4" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>37</v>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2B56A3-7028-4E68-9B61-925ACEEE7224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA28A7C-A080-4DB4-8B61-0BC273E5C760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -127,9 +127,6 @@
     <t>Program</t>
   </si>
   <si>
-    <t>Application</t>
-  </si>
-  <si>
     <t>Automation Runtime Site Visit Org level</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>fieldSiteVisitType__c</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -555,10 +555,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,7 +577,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -588,7 +588,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>27</v>
@@ -627,7 +627,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -638,10 +638,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -649,7 +649,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -660,14 +660,15 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -697,7 +698,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -708,7 +709,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
@@ -719,7 +720,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -730,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -741,7 +742,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -752,7 +753,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -763,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -801,7 +802,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -812,7 +813,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1">
         <v>20</v>
@@ -823,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -834,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -845,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
@@ -1008,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1019,10 +1020,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1030,7 +1031,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>30</v>
@@ -1041,10 +1042,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1079,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1090,10 +1091,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1101,7 +1102,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1112,10 +1113,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1150,7 +1151,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1161,10 +1162,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1172,7 +1173,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1183,7 +1184,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>27</v>
